--- a/artfynd/S 4819-2024 artfynd.xlsx
+++ b/artfynd/S 4819-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY36"/>
+  <dimension ref="A1:AZ36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105162137</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -870,6 +880,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118469079</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -967,6 +982,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118469091</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1064,6 +1084,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118469093</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1161,6 +1186,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119446534</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1258,6 +1288,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119446745</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1355,6 +1390,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119446764</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1452,6 +1492,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119446786</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1553,6 +1598,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105162140</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1650,6 +1700,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118469087</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1748,6 +1803,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103813496</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1849,6 +1909,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105162128</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1946,6 +2011,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118469092</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2047,6 +2117,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105162120</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2148,6 +2223,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105162123</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2254,6 +2334,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105162124</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2355,6 +2440,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105162130</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2456,6 +2546,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105162134</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2557,6 +2652,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105162138</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2658,6 +2758,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105162153</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2755,6 +2860,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118469099</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2852,6 +2962,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119446729</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2953,6 +3068,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105162131</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3059,6 +3179,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105162132</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3165,6 +3290,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105162133</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3262,6 +3392,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118469090</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3359,6 +3494,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118469097</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3456,6 +3596,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118469095</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3559,6 +3704,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103811349</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3662,6 +3812,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103813605</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3768,6 +3923,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105162126</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3874,6 +4034,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105162155</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3971,6 +4136,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118469088</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4069,6 +4239,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103811406</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4170,8 +4345,50 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105162154</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>